--- a/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,67; 44,14</t>
+          <t>26,48; 43,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 31,48</t>
+          <t>12,87; 30,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -6,83</t>
+          <t>-21,38; -6,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,72; 31,75</t>
+          <t>13,9; 32,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 24,83</t>
+          <t>4,48; 23,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -15,88</t>
+          <t>-31,94; -16,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,69; 35,72</t>
+          <t>21,76; 35,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 25,17</t>
+          <t>11,23; 25,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-24,5; -13,84</t>
+          <t>-24,41; -13,42</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,07; 234,95</t>
+          <t>91,63; 232,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,23; 157,39</t>
+          <t>45,88; 167,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,14; -35,02</t>
+          <t>-74,85; -32,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,3; 107,08</t>
+          <t>33,16; 109,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 83,21</t>
+          <t>10,72; 79,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,73; -53,72</t>
+          <t>-75,39; -52,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,62; 136,47</t>
+          <t>61,27; 134,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,31; 95,96</t>
+          <t>33,39; 98,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,24; -52,18</t>
+          <t>-72,24; -52,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,27; 35,67</t>
+          <t>21,74; 35,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 6,5</t>
+          <t>-5,02; 6,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 7,59</t>
+          <t>-4,79; 7,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,67; 35,8</t>
+          <t>22,67; 35,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 5,77</t>
+          <t>-6,7; 4,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 8,81</t>
+          <t>-2,56; 8,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,67; 33,7</t>
+          <t>23,88; 32,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,11</t>
+          <t>-4,56; 4,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 6,47</t>
+          <t>-1,83; 6,63</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,63; 218,41</t>
+          <t>98,51; 220,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 38,72</t>
+          <t>-22,95; 38,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 46,07</t>
+          <t>-22,59; 45,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,53; 172,13</t>
+          <t>84,41; 169,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 27,94</t>
+          <t>-24,81; 22,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 43,0</t>
+          <t>-9,62; 40,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>102,84; 173,56</t>
+          <t>99,03; 169,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 20,2</t>
+          <t>-19,36; 20,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 33,65</t>
+          <t>-8,03; 33,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,09; 37,18</t>
+          <t>21,4; 37,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 13,01</t>
+          <t>-0,17; 14,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 6,44</t>
+          <t>-6,33; 7,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,63; 31,32</t>
+          <t>14,55; 30,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 6,41</t>
+          <t>-8,57; 7,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -2,16</t>
+          <t>-15,68; -1,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,61; 31,85</t>
+          <t>20,68; 32,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 7,17</t>
+          <t>-3,02; 7,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 0,45</t>
+          <t>-9,68; 0,07</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,31; 244,32</t>
+          <t>90,42; 261,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 84,96</t>
+          <t>-1,48; 101,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 41,91</t>
+          <t>-28,04; 49,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,11; 113,23</t>
+          <t>40,77; 113,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 23,56</t>
+          <t>-24,65; 27,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,01; -7,07</t>
+          <t>-43,76; -5,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,47; 136,79</t>
+          <t>74,38; 144,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 32,1</t>
+          <t>-10,77; 31,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 2,08</t>
+          <t>-32,93; 0,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,46; 50,25</t>
+          <t>35,92; 51,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,98; 33,95</t>
+          <t>18,31; 33,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 21,18</t>
+          <t>5,79; 22,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32,32; 46,64</t>
+          <t>31,47; 45,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,36; 30,68</t>
+          <t>16,16; 30,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 4,12</t>
+          <t>-13,8; 4,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,9; 45,98</t>
+          <t>35,96; 45,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,97; 30,11</t>
+          <t>19,82; 30,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 9,06</t>
+          <t>-5,09; 9,23</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>198,55; 451,89</t>
+          <t>199,3; 456,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>105,37; 299,2</t>
+          <t>102,83; 292,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,67; 172,84</t>
+          <t>29,79; 194,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>118,47; 236,74</t>
+          <t>113,81; 227,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>63,17; 155,53</t>
+          <t>58,64; 153,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 18,4</t>
+          <t>-54,32; 21,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>163,39; 274,67</t>
+          <t>162,54; 274,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92,46; 175,75</t>
+          <t>88,94; 181,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 50,11</t>
+          <t>-24,56; 51,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,3; 36,5</t>
+          <t>15,55; 36,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,45; 41,73</t>
+          <t>22,64; 42,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 5,77</t>
+          <t>-13,15; 6,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,85; 38,93</t>
+          <t>21,15; 40,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,21; 49,68</t>
+          <t>30,28; 49,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 0,91</t>
+          <t>-20,31; 1,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,56; 36,04</t>
+          <t>21,45; 35,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,54; 42,87</t>
+          <t>29,61; 43,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,44; -0,3</t>
+          <t>-17,6; -0,51</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45,13; 168,65</t>
+          <t>45,89; 159,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>63,31; 192,4</t>
+          <t>67,16; 189,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 25,94</t>
+          <t>-41,23; 27,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69,88; 208,17</t>
+          <t>65,47; 207,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>104,28; 263,91</t>
+          <t>101,23; 257,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,02; 4,26</t>
+          <t>-71,9; 4,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,24; 161,77</t>
+          <t>73,32; 158,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>100,96; 196,83</t>
+          <t>98,39; 198,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,79; -1,47</t>
+          <t>-60,34; -2,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>28,91; 45,47</t>
+          <t>29,49; 45,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18,77; 36,77</t>
+          <t>18,8; 36,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,6; 20,36</t>
+          <t>6,0; 20,99</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18,25; 35,05</t>
+          <t>17,55; 34,36</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,04; 32,33</t>
+          <t>14,56; 32,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,79; 20,94</t>
+          <t>5,46; 19,94</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,68; 37,35</t>
+          <t>25,93; 37,62</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>18,9; 31,55</t>
+          <t>19,11; 30,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,22</t>
+          <t>7,96; 18,47</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>144,04; 401,2</t>
+          <t>153,67; 406,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>98,96; 321,1</t>
+          <t>100,24; 306,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29,93; 187,75</t>
+          <t>29,42; 175,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>69,36; 205,01</t>
+          <t>67,69; 207,31</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>53,25; 187,94</t>
+          <t>57,64; 200,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22,43; 126,47</t>
+          <t>21,73; 118,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>120,26; 244,88</t>
+          <t>120,44; 242,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>90,99; 201,94</t>
+          <t>90,7; 199,76</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36,16; 115,43</t>
+          <t>36,85; 119,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>21,91; 34,29</t>
+          <t>21,27; 33,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,03; 22,17</t>
+          <t>9,95; 22,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,58; -2,85</t>
+          <t>-13,14; -2,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15,98; 26,88</t>
+          <t>16,14; 27,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,86; 23,88</t>
+          <t>12,64; 23,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 50,17</t>
+          <t>-14,3; 48,8</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,06; 28,0</t>
+          <t>20,39; 28,14</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>13,14; 21,69</t>
+          <t>13,07; 21,92</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 41,01</t>
+          <t>-11,6; 37,89</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>94,19; 201,42</t>
+          <t>92,85; 201,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>39,1; 129,6</t>
+          <t>42,64; 133,39</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,67; -14,55</t>
+          <t>-58,65; -15,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54,91; 113,98</t>
+          <t>54,45; 115,67</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>41,75; 100,07</t>
+          <t>43,23; 102,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 222,91</t>
+          <t>-52,79; 203,0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76,63; 131,14</t>
+          <t>79,38; 130,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>51,49; 101,38</t>
+          <t>51,16; 103,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 178,92</t>
+          <t>-48,98; 160,02</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>16,26; 27,94</t>
+          <t>17,2; 27,98</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>24,59; 35,46</t>
+          <t>25,06; 36,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,8; 15,05</t>
+          <t>4,46; 15,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>25,31; 35,53</t>
+          <t>24,5; 34,65</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>34,21; 44,79</t>
+          <t>33,73; 44,07</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,25; 26,56</t>
+          <t>16,49; 26,41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,64; 30,21</t>
+          <t>22,46; 30,2</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>31,47; 38,72</t>
+          <t>31,27; 38,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12,0; 20,03</t>
+          <t>12,18; 19,92</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>49,3; 104,46</t>
+          <t>52,86; 105,17</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>74,33; 132,54</t>
+          <t>76,95; 143,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11,33; 55,72</t>
+          <t>13,0; 58,38</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>87,99; 150,41</t>
+          <t>86,67; 152,02</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>120,16; 193,21</t>
+          <t>115,43; 183,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>57,44; 115,28</t>
+          <t>55,38; 111,33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>75,49; 115,04</t>
+          <t>74,68; 116,77</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>103,97; 148,35</t>
+          <t>105,0; 152,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>39,8; 75,95</t>
+          <t>40,22; 76,7</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>27,45; 32,49</t>
+          <t>27,2; 32,3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>17,05; 22,27</t>
+          <t>17,23; 22,45</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,51</t>
+          <t>-1,1; 3,61</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25,42; 30,36</t>
+          <t>25,58; 30,47</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>18,14; 23,18</t>
+          <t>18,41; 23,39</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 20,34</t>
+          <t>-1,32; 22,42</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,12; 30,64</t>
+          <t>27,11; 30,69</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>18,53; 22,07</t>
+          <t>18,61; 22,06</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 13,71</t>
+          <t>-0,44; 13,45</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>119,86; 159,06</t>
+          <t>116,73; 157,04</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>73,94; 108,89</t>
+          <t>74,92; 109,56</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 17,22</t>
+          <t>-5,03; 17,72</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>92,78; 122,01</t>
+          <t>93,03; 121,8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>66,52; 92,55</t>
+          <t>67,15; 93,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 76,87</t>
+          <t>-5,01; 87,69</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>107,43; 131,19</t>
+          <t>108,24; 132,25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>73,85; 94,31</t>
+          <t>74,07; 94,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 55,7</t>
+          <t>-1,95; 58,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-14,04</t>
+          <t>-13,73</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-23,61</t>
+          <t>-22,98</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-18,94</t>
+          <t>-18,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,48; 43,92</t>
+          <t>25,96; 44,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 30,91</t>
+          <t>13,19; 31,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -6,34</t>
+          <t>-22,04; -7,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 32,87</t>
+          <t>14,22; 33,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 23,99</t>
+          <t>5,23; 24,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,94; -16,08</t>
+          <t>-31,2; -15,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,76; 35,3</t>
+          <t>22,55; 35,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,23; 25,36</t>
+          <t>11,62; 25,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-24,41; -13,42</t>
+          <t>-23,86; -13,41</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-58,61%</t>
+          <t>-57,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-65,73%</t>
+          <t>-63,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-63,02%</t>
+          <t>-61,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,63; 232,64</t>
+          <t>86,58; 233,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,88; 167,49</t>
+          <t>45,49; 168,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,85; -32,53</t>
+          <t>-72,8; -37,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,16; 109,18</t>
+          <t>34,06; 109,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 79,96</t>
+          <t>11,9; 80,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,39; -52,82</t>
+          <t>-73,69; -50,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,27; 134,93</t>
+          <t>66,04; 135,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 98,19</t>
+          <t>33,65; 92,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,24; -52,15</t>
+          <t>-70,42; -50,12</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>3,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,74; 35,61</t>
+          <t>22,23; 36,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 6,06</t>
+          <t>-5,01; 6,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 7,53</t>
+          <t>-3,99; 9,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,67; 35,19</t>
+          <t>22,52; 35,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 4,63</t>
+          <t>-6,29; 5,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 8,74</t>
+          <t>-1,1; 9,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,88; 32,97</t>
+          <t>24,35; 33,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 4,07</t>
+          <t>-4,19; 3,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,63</t>
+          <t>-0,62; 7,27</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>98,51; 220,67</t>
+          <t>97,31; 226,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 38,43</t>
+          <t>-22,8; 43,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 45,55</t>
+          <t>-18,19; 60,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,41; 169,2</t>
+          <t>83,55; 164,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 22,27</t>
+          <t>-23,09; 25,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 40,28</t>
+          <t>-4,01; 45,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03; 169,66</t>
+          <t>100,12; 168,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 20,83</t>
+          <t>-17,55; 19,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 33,4</t>
+          <t>-2,61; 36,47</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,59</t>
+          <t>-9,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,53</t>
+          <t>-4,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 37,78</t>
+          <t>21,68; 37,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 14,41</t>
+          <t>-0,89; 13,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 7,35</t>
+          <t>-6,94; 7,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 30,86</t>
+          <t>15,6; 31,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 7,38</t>
+          <t>-8,92; 6,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,68; -1,38</t>
+          <t>-15,59; -2,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,68; 32,31</t>
+          <t>20,39; 31,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 7,34</t>
+          <t>-4,25; 7,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 0,07</t>
+          <t>-9,79; 0,09</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,18%</t>
+          <t>-29,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,61%</t>
+          <t>-18,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,42; 261,9</t>
+          <t>89,33; 250,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 101,54</t>
+          <t>-4,57; 87,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 49,2</t>
+          <t>-29,78; 46,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40,77; 113,8</t>
+          <t>43,63; 115,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 27,48</t>
+          <t>-26,1; 22,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,76; -5,28</t>
+          <t>-45,13; -8,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74,38; 144,96</t>
+          <t>71,13; 138,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 31,96</t>
+          <t>-14,92; 34,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 0,74</t>
+          <t>-34,98; 0,14</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13,59</t>
+          <t>14,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>8,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,92; 51,0</t>
+          <t>36,23; 50,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,31; 33,01</t>
+          <t>18,77; 33,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 22,3</t>
+          <t>6,67; 22,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,47; 45,34</t>
+          <t>32,2; 46,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,16; 30,91</t>
+          <t>16,44; 31,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 4,87</t>
+          <t>-3,55; 9,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,96; 45,86</t>
+          <t>36,27; 45,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,82; 30,66</t>
+          <t>19,41; 29,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 9,23</t>
+          <t>3,03; 13,16</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-16,28%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>199,3; 456,84</t>
+          <t>201,1; 454,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>102,83; 292,58</t>
+          <t>103,6; 291,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,79; 194,3</t>
+          <t>37,65; 190,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113,81; 227,1</t>
+          <t>117,56; 237,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,64; 153,37</t>
+          <t>61,9; 156,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,32; 21,1</t>
+          <t>-13,56; 48,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>162,54; 274,61</t>
+          <t>162,93; 271,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88,94; 181,73</t>
+          <t>90,47; 177,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 51,91</t>
+          <t>13,48; 75,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,05</t>
+          <t>-3,07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,86</t>
+          <t>-1,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,9</t>
+          <t>-2,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,55; 36,26</t>
+          <t>14,81; 36,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,64; 42,69</t>
+          <t>21,66; 42,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 6,39</t>
+          <t>-13,1; 7,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,15; 40,25</t>
+          <t>21,18; 40,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,28; 49,44</t>
+          <t>30,05; 49,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 1,35</t>
+          <t>-9,86; 6,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,45; 35,33</t>
+          <t>21,28; 35,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29,61; 43,46</t>
+          <t>29,42; 43,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -0,51</t>
+          <t>-8,86; 3,04</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-14,85%</t>
+          <t>-11,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-32,36%</t>
+          <t>-7,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-26,92%</t>
+          <t>-9,66%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45,89; 159,73</t>
+          <t>44,06; 165,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>67,16; 189,77</t>
+          <t>65,47; 196,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 27,78</t>
+          <t>-40,66; 31,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65,47; 207,58</t>
+          <t>70,64; 212,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>101,23; 257,98</t>
+          <t>97,46; 256,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,9; 4,53</t>
+          <t>-33,42; 33,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,32; 158,46</t>
+          <t>71,03; 162,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>98,39; 198,31</t>
+          <t>98,59; 202,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-60,34; -2,32</t>
+          <t>-30,43; 13,04</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13,29</t>
+          <t>14,36</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,94</t>
+          <t>12,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,06</t>
+          <t>13,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>29,49; 45,92</t>
+          <t>28,95; 46,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18,8; 36,03</t>
+          <t>19,27; 36,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,0; 20,99</t>
+          <t>7,48; 21,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17,55; 34,36</t>
+          <t>18,02; 34,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,56; 32,25</t>
+          <t>14,28; 33,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,46; 19,94</t>
+          <t>4,54; 18,47</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,93; 37,62</t>
+          <t>25,54; 37,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>19,11; 30,92</t>
+          <t>18,83; 31,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,96; 18,47</t>
+          <t>8,51; 18,43</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>74,52%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>153,67; 406,33</t>
+          <t>149,96; 402,43</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>100,24; 306,4</t>
+          <t>98,32; 307,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29,42; 175,43</t>
+          <t>36,71; 183,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67,69; 207,31</t>
+          <t>67,55; 205,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>57,64; 200,2</t>
+          <t>56,2; 194,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,73; 118,15</t>
+          <t>17,45; 107,97</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>120,44; 242,24</t>
+          <t>120,74; 245,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>90,7; 199,76</t>
+          <t>92,02; 206,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36,85; 119,62</t>
+          <t>39,37; 119,94</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-8,31</t>
+          <t>-7,85</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>-11,86</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>-10,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>21,27; 33,3</t>
+          <t>21,33; 34,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,95; 22,34</t>
+          <t>9,89; 22,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -2,78</t>
+          <t>-13,0; -2,83</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16,14; 27,14</t>
+          <t>15,71; 27,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,64; 23,93</t>
+          <t>12,37; 24,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 48,8</t>
+          <t>-16,29; -7,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,39; 28,14</t>
+          <t>20,05; 28,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>13,07; 21,92</t>
+          <t>13,4; 21,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 37,89</t>
+          <t>-13,42; -6,52</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-41,36%</t>
+          <t>-39,08%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>-45,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>-42,97%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>92,85; 201,17</t>
+          <t>88,94; 206,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>42,64; 133,39</t>
+          <t>42,24; 125,66</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,65; -15,66</t>
+          <t>-57,06; -16,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54,45; 115,67</t>
+          <t>53,19; 114,75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>43,23; 102,0</t>
+          <t>41,31; 100,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 203,0</t>
+          <t>-56,26; -31,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>79,38; 130,49</t>
+          <t>78,47; 132,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>51,16; 103,13</t>
+          <t>53,02; 102,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-48,98; 160,02</t>
+          <t>-52,18; -30,43</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>11,55</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>22,56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16,08</t>
+          <t>17,58</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>17,2; 27,98</t>
+          <t>16,73; 28,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>25,06; 36,7</t>
+          <t>24,35; 35,64</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,46; 15,84</t>
+          <t>5,12; 17,49</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>24,5; 34,65</t>
+          <t>24,79; 34,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>33,73; 44,07</t>
+          <t>34,37; 44,49</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,49; 26,41</t>
+          <t>17,72; 27,47</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,46; 30,2</t>
+          <t>22,52; 30,46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>31,27; 38,9</t>
+          <t>31,31; 38,79</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12,18; 19,92</t>
+          <t>13,8; 21,42</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>63,09%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>52,86; 105,17</t>
+          <t>50,57; 104,31</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>76,95; 143,0</t>
+          <t>70,64; 130,87</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13,0; 58,38</t>
+          <t>16,11; 64,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>86,67; 152,02</t>
+          <t>86,07; 148,28</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>115,43; 183,17</t>
+          <t>119,46; 190,27</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,38; 111,33</t>
+          <t>61,12; 115,51</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>74,68; 116,77</t>
+          <t>75,47; 116,75</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>105,0; 152,92</t>
+          <t>105,16; 149,78</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>40,22; 76,7</t>
+          <t>47,38; 83,87</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>27,2; 32,3</t>
+          <t>27,12; 32,6</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>17,23; 22,45</t>
+          <t>17,05; 22,44</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,61</t>
+          <t>-0,45; 4,65</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25,58; 30,47</t>
+          <t>25,8; 30,42</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,39</t>
+          <t>18,2; 23,1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 22,42</t>
+          <t>-0,67; 3,66</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,11; 30,69</t>
+          <t>26,97; 30,5</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>18,61; 22,06</t>
+          <t>18,25; 21,98</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 13,45</t>
+          <t>0,25; 3,48</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>116,73; 157,04</t>
+          <t>117,32; 159,14</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>74,92; 109,56</t>
+          <t>73,49; 108,72</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 17,72</t>
+          <t>-1,61; 22,91</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>93,03; 121,8</t>
+          <t>93,74; 123,11</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>67,15; 93,4</t>
+          <t>66,44; 92,38</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 87,69</t>
+          <t>-2,43; 14,72</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>108,24; 132,25</t>
+          <t>107,28; 131,06</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>74,07; 94,77</t>
+          <t>73,18; 94,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 58,2</t>
+          <t>0,97; 14,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
